--- a/Sindhi Muslim/Result Sheet/Class 1 - Students Result Sheet.xlsx
+++ b/Sindhi Muslim/Result Sheet/Class 1 - Students Result Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD7FB2-45F5-49AA-B9BE-66E79050BF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB58480-BBB8-4739-8CE2-FC0C9C46B326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
   </bookViews>
@@ -1106,7 +1106,7 @@
       <c r="O4" s="19"/>
       <c r="P4" s="19"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>

--- a/Sindhi Muslim/Result Sheet/Class 1 - Students Result Sheet.xlsx
+++ b/Sindhi Muslim/Result Sheet/Class 1 - Students Result Sheet.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB58480-BBB8-4739-8CE2-FC0C9C46B326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF4A0EE-AEE0-44F5-861B-DA27075783C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
   </bookViews>
   <sheets>
-    <sheet name="ECE (ROSE)" sheetId="1" r:id="rId1"/>
+    <sheet name="One" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ECE (ROSE)'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">One!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
